--- a/produtos.xlsx
+++ b/produtos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24000" windowHeight="10095"/>
+    <workbookView windowWidth="24000" windowHeight="10815"/>
   </bookViews>
   <sheets>
     <sheet name="Produtos" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="72">
   <si>
     <t>id</t>
   </si>
@@ -57,6 +57,24 @@
     <t>disponivel</t>
   </si>
   <si>
+    <t>largura_cm</t>
+  </si>
+  <si>
+    <t>altura_cm</t>
+  </si>
+  <si>
+    <t>profundidade_cm</t>
+  </si>
+  <si>
+    <t>imagem_1</t>
+  </si>
+  <si>
+    <t>imagem_2</t>
+  </si>
+  <si>
+    <t>imagem_3</t>
+  </si>
+  <si>
     <t>Sofá Retrátil 3 Lugares Premium</t>
   </si>
   <si>
@@ -208,6 +226,24 @@
   </si>
   <si>
     <t>Após salvar o Excel, recarregue a página do site no navegador</t>
+  </si>
+  <si>
+    <t>Largura do produto em centímetros (ex: 220)</t>
+  </si>
+  <si>
+    <t>Altura do produto em centímetros (ex: 95)</t>
+  </si>
+  <si>
+    <t>Profundidade/comprimento do produto em centímetros (ex: 100)</t>
+  </si>
+  <si>
+    <t>URL da segunda imagem do produto (para carrossel)</t>
+  </si>
+  <si>
+    <t>URL da terceira imagem do produto (para carrossel)</t>
+  </si>
+  <si>
+    <t>URL da quarta imagem do produto (para carrossel)</t>
   </si>
 </sst>
 </file>
@@ -221,7 +257,7 @@
     <numFmt numFmtId="179" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="180" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -256,6 +292,13 @@
       <b/>
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -748,152 +791,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -915,6 +958,7 @@
     <xf numFmtId="180" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1268,18 +1312,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="35" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="5" width="12" customWidth="1"/>
-    <col min="6" max="7" width="60" customWidth="1"/>
-    <col min="8" max="9" width="12" customWidth="1"/>
+    <col min="1" max="1" width="3.57142857142857" customWidth="1"/>
+    <col min="2" max="2" width="36" customWidth="1"/>
+    <col min="3" max="3" width="12.8571428571429" customWidth="1"/>
+    <col min="4" max="4" width="11.4285714285714" customWidth="1"/>
+    <col min="5" max="5" width="15.1428571428571" customWidth="1"/>
+    <col min="6" max="6" width="121" customWidth="1"/>
+    <col min="7" max="7" width="74.1428571428571" customWidth="1"/>
+    <col min="8" max="8" width="10.5714285714286" customWidth="1"/>
+    <col min="9" max="9" width="11.7142857142857" customWidth="1"/>
+    <col min="10" max="10" width="11.4285714285714" customWidth="1"/>
+    <col min="11" max="11" width="10.2857142857143" customWidth="1"/>
+    <col min="12" max="12" width="18.1428571428571" customWidth="1"/>
+    <col min="13" max="15" width="10.8571428571429" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:9">
+    <row r="1" ht="30" customHeight="1" spans="1:15">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1307,16 +1358,34 @@
       <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" s="5">
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D2" s="7">
         <v>2890</v>
@@ -1325,16 +1394,25 @@
         <v>3490</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>13</v>
+        <v>19</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -1342,10 +1420,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D3" s="10">
         <v>4290</v>
@@ -1354,16 +1432,16 @@
         <v>5200</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -1371,10 +1449,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D4" s="7">
         <v>3190</v>
@@ -1383,16 +1461,16 @@
         <v>3800</v>
       </c>
       <c r="F4" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>13</v>
-      </c>
       <c r="I4" s="6" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -1400,10 +1478,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D5" s="10">
         <v>1290</v>
@@ -1412,16 +1490,16 @@
         <v>1590</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -1429,10 +1507,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D6" s="7">
         <v>1890</v>
@@ -1441,16 +1519,16 @@
         <v>2290</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -1458,10 +1536,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D7" s="10">
         <v>890</v>
@@ -1470,16 +1548,16 @@
         <v>1100</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -1487,10 +1565,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D8" s="7">
         <v>1490</v>
@@ -1499,16 +1577,16 @@
         <v>1890</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -1516,10 +1594,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D9" s="10">
         <v>2190</v>
@@ -1528,16 +1606,16 @@
         <v>2700</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -1545,10 +1623,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D10" s="10">
         <v>890</v>
@@ -1557,16 +1635,16 @@
         <v>1100</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -1574,10 +1652,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D11" s="10">
         <v>890</v>
@@ -1586,16 +1664,16 @@
         <v>1100</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -1603,10 +1681,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D12" s="10">
         <v>890</v>
@@ -1615,16 +1693,16 @@
         <v>1100</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1636,35 +1714,35 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75" spans="1:2">
+    <row r="1" ht="18.75" customHeight="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B2" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1672,7 +1750,7 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1680,7 +1758,7 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1688,7 +1766,7 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1696,7 +1774,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1704,7 +1782,7 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1712,7 +1790,7 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1720,7 +1798,7 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1728,7 +1806,7 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1736,55 +1814,103 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B14" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="3" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="B15" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="3" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B16" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="3" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B17" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="3" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="B18" t="s">
-        <v>59</v>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>10</v>
+      </c>
+      <c r="B21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
